--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-practitioner.xlsx
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -314,16 +314,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -449,7 +449,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -633,7 +633,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -653,7 +653,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Practitioner.telecom.system</t>
@@ -671,7 +671,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「連絡先のための通信フォーム。」</t>
+    <t>連絡先のための通信フォーム。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-system|4.0.1</t>
@@ -730,7 +730,7 @@
     <t>home | work | temp | old | mobile - 連絡先の用途等 【JP_Patient.telecomを参照。】</t>
   </si>
   <si>
-    <t>「接点の目的を特定する。」(Setten no mokuteki wo tokutei suru.)</t>
+    <t>「接点の目的を特定する。」</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。  一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -744,7 +744,7 @@
     <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
-    <t>「接点の使用。」(Setten no shiyō.)</t>
+    <t>「接点の使用。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.0.1</t>
@@ -769,10 +769,10 @@
 </t>
   </si>
   <si>
-    <t>「使用の優先順位を指定してください（1が最も優先度が高い）」</t>
-  </si>
-  <si>
-    <t>「一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。」</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い）</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -788,10 +788,10 @@
 </t>
   </si>
   <si>
-    <t>「コンタクトポイントが使用されている時間帯」</t>
-  </si>
-  <si>
-    <t>「接点が使用されていた/現在使用中である時間期間」</t>
+    <t>コンタクトポイントが使用されている時間帯</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1120,7 +1120,7 @@
     <t>住所が使用されていた/されている期間。 期間は時間の範囲を指定する。使用状況はその期間全体に適用されるか、範囲から1つの値が適用される。  期間は、時間間隔（経過時間の測定値）には使用されない。</t>
   </si>
   <si>
-    <t>アドレスを歴史的な文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
+    <t>アドレスを履歴上の文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
   </si>
   <si>
     <t>Address.period</t>
@@ -1264,7 +1264,7 @@
     <t>Practitioner.qualification.identifier</t>
   </si>
   <si>
-    <t>開業医のこの資格の識別子 / An identifier for this qualification for the practitioner</t>
+    <t>開業医のこの資格のidentifier / An identifier for this qualification for the practitioner</t>
   </si>
   <si>
     <t>この人物のこの役割における資格に適用される識別子。</t>
@@ -1383,7 +1383,7 @@
     <t>都道府県別 麻薬施用者免許番号</t>
   </si>
   <si>
-    <t>この役割におけるこの人の資格に適用される識別子。 / An identifier that applies to this person's qualification in this role.</t>
+    <t>この役割におけるこの人の資格に適用されるidentifier。 / An identifier that applies to this person's qualification in this role.</t>
   </si>
   <si>
     <t>多くの場合、資格に特定のIDが割り当てられます。 / Often, specific identities are assigned for the qualification.</t>
@@ -1407,19 +1407,19 @@
     <t>Practitioner.qualification.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -1437,22 +1437,22 @@
     <t>Practitioner.qualification.identifier.type</t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -1527,7 +1527,7 @@
 　- urn:oid:1.2.392.100495.20.3.32.147(沖縄県)</t>
   </si>
   <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -1551,7 +1551,7 @@
     <t>都道府県別　麻薬施用者免許番号 【詳細参照】</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
     <t>都道府県別　麻薬施用者免許番号</t>
@@ -1575,7 +1575,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -1600,10 +1600,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -1686,13 +1686,13 @@
     <t>Practitioner.qualification:medicalRegistrationNumber.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber</t>
@@ -2076,7 +2076,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="60.75390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
